--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:14</t>
+    <t xml:space="preserve">2026-09-09 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$16</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -59,6 +59,9 @@
     <t xml:space="preserve">Antártica Chilena</t>
   </si>
   <si>
+    <t xml:space="preserve">Promedio Regional</t>
+  </si>
+  <si>
     <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
@@ -71,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:12</t>
+    <t xml:space="preserve">2026-09-17 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +533,7 @@
         <v>-2.24</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +556,7 @@
         <v>2.38</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -576,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +602,7 @@
         <v>-5.62</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +625,7 @@
         <v>-5.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +648,7 @@
         <v>-5.36</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -668,7 +671,7 @@
         <v>1.9</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -691,7 +694,7 @@
         <v>0.95</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +717,7 @@
         <v>1.56</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -725,19 +728,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13.49</v>
+        <v>12.88</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13.64</v>
+        <v>13.11</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.75</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -748,19 +751,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7.06</v>
+        <v>7.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.55</v>
+        <v>1.26</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -771,23 +774,92 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>9.86</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>10.09</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D16" s="2" t="n">
         <v>10.08</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -804,58 +876,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -878,23 +950,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.11</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>10.09</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="4">
@@ -935,76 +1007,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8.97</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9.11</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8.25</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10.08</v>
+        <v>8.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10.09</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9.86</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="8">
@@ -1012,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>8.11</v>
@@ -1023,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>8.11</v>
@@ -1034,7 +1106,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>8.93</v>
@@ -1045,7 +1117,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>9.33</v>
@@ -1056,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>8.83</v>
@@ -1067,14 +1139,47 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>8.53</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>9.86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>9.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:41</t>
+    <t xml:space="preserve">2026-09-25 21:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>-0.21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2.24</v>
+        <v>-2.28</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>-0.66</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5.62</v>
+        <v>-5.58</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -619,10 +619,10 @@
         <v>7.36</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5.3</v>
+        <v>-5.19</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-0.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-5.36</v>
+        <v>-5.38</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>0.18</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -691,7 +691,7 @@
         <v>0.08</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>0.14</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-0.23</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1.75</v>
+        <v>-1.76</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>0.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.06</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -829,7 +829,7 @@
         <v>0.18</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -849,10 +849,10 @@
         <v>10.08</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_magallanes.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
